--- a/feedback_forms/023_holiday_movie_ranking_survey--feedback_forms.xlsx
+++ b/feedback_forms/023_holiday_movie_ranking_survey--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1133,8 +1133,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'elf'}</t>
+          <t>elf</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Elf'}</t>
+          <t>Elf</t>
         </is>
       </c>
     </row>
@@ -1179,12 +1179,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_"it's_a_wonderful_life"}</t>
+          <t>it's_a_wonderful_life</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': "It's a Wonderful Life"}</t>
+          <t>It's a Wonderful Life</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'a_christmas_carol'}</t>
+          <t>a_christmas_carol</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'A Christmas Carol'}</t>
+          <t>A Christmas Carol</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_"national_lampoon's_christmas"}</t>
+          <t>national_lampoon's_christmas</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': "National Lampoon's Christmas"}</t>
+          <t>National Lampoon's Christmas</t>
         </is>
       </c>
     </row>
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'chartinstance'}</t>
+          <t>chartinstance</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'chartInstance'}</t>
+          <t>chartInstance</t>
         </is>
       </c>
     </row>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'love_actually'}</t>
+          <t>love_actually</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Love Actually'}</t>
+          <t>Love Actually</t>
         </is>
       </c>
     </row>
@@ -1264,12 +1264,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'the_santa_clause_3'}</t>
+          <t>the_santa_clause_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'The Santa Clause 3'}</t>
+          <t>The Santa Clause 3</t>
         </is>
       </c>
     </row>
@@ -1281,12 +1281,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'jingle_all_the_way'}</t>
+          <t>jingle_all_the_way</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Jingle All the Way'}</t>
+          <t>Jingle All the Way</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'the_polar_express'}</t>
+          <t>the_polar_express</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'The Polar Express'}</t>
+          <t>The Polar Express</t>
         </is>
       </c>
     </row>
